--- a/reports/Debug-purgatory-20260105/For The Week Ending (Actual)_Budget_week_total.xlsx
+++ b/reports/Debug-purgatory-20260105/For The Week Ending (Actual)_Budget_week_total.xlsx
@@ -19,6 +19,39 @@
     <t>Department</t>
   </si>
   <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>99100</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D2200</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D5202</t>
+  </si>
+  <si>
+    <t>D5209</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>99200</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
     <t>D1020</t>
   </si>
   <si>
@@ -55,6 +88,30 @@
     <t>D8040</t>
   </si>
   <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4054</t>
+  </si>
+  <si>
+    <t>D5206</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6720</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D6800</t>
+  </si>
+  <si>
     <t>D1010</t>
   </si>
   <si>
@@ -88,39 +145,6 @@
     <t>D8060</t>
   </si>
   <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4054</t>
-  </si>
-  <si>
-    <t>D5206</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6720</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D6800</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>99200</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
     <t>D1030</t>
   </si>
   <si>
@@ -133,39 +157,15 @@
     <t>D5810</t>
   </si>
   <si>
-    <t>99100</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D2200</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D5202</t>
-  </si>
-  <si>
-    <t>D5209</t>
-  </si>
-  <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
+    <t>Revenue</t>
+  </si>
+  <si>
     <t>Payroll</t>
   </si>
   <si>
-    <t>Revenue</t>
-  </si>
-  <si>
     <t>Visits</t>
   </si>
   <si>
@@ -175,6 +175,39 @@
     <t>DepartmentTitle</t>
   </si>
   <si>
+    <t>Grounds Maintenance</t>
+  </si>
+  <si>
+    <t>Daily Winter Ticketed</t>
+  </si>
+  <si>
+    <t>Ski School</t>
+  </si>
+  <si>
+    <t>Child Care</t>
+  </si>
+  <si>
+    <t>Rentals</t>
+  </si>
+  <si>
+    <t>Dante's</t>
+  </si>
+  <si>
+    <t>Village Market Deli</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>Winter Season Pass Visits  - Home Resort</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
     <t>Lift Maintenance</t>
   </si>
   <si>
@@ -211,6 +244,30 @@
     <t>HR</t>
   </si>
   <si>
+    <t>Mountain G&amp;A</t>
+  </si>
+  <si>
+    <t>Purg Sports Resort</t>
+  </si>
+  <si>
+    <t>Hoody's</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Guest Services</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Commercial Tenants</t>
+  </si>
+  <si>
     <t>Lift Operations</t>
   </si>
   <si>
@@ -244,39 +301,6 @@
     <t>IT Services</t>
   </si>
   <si>
-    <t>Mountain G&amp;A</t>
-  </si>
-  <si>
-    <t>Purg Sports Resort</t>
-  </si>
-  <si>
-    <t>Hoody's</t>
-  </si>
-  <si>
-    <t>Resort Services G&amp;A</t>
-  </si>
-  <si>
-    <t>Guest Services</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Commercial Tenants</t>
-  </si>
-  <si>
-    <t>Grounds Maintenance</t>
-  </si>
-  <si>
-    <t>Winter Season Pass Visits  - Home Resort</t>
-  </si>
-  <si>
-    <t>Risk Management</t>
-  </si>
-  <si>
     <t>Snowmaking</t>
   </si>
   <si>
@@ -287,30 +311,6 @@
   </si>
   <si>
     <t>Events</t>
-  </si>
-  <si>
-    <t>Daily Winter Ticketed</t>
-  </si>
-  <si>
-    <t>Ski School</t>
-  </si>
-  <si>
-    <t>Child Care</t>
-  </si>
-  <si>
-    <t>Rentals</t>
-  </si>
-  <si>
-    <t>Dante's</t>
-  </si>
-  <si>
-    <t>Village Market Deli</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Accounting</t>
   </si>
 </sst>
 </file>
@@ -704,7 +704,7 @@
         <v>48</v>
       </c>
       <c r="C2" s="2">
-        <v>14457.75</v>
+        <v>2956.97</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>53</v>
@@ -712,366 +712,366 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2">
-        <v>16444.30</v>
+        <v>12779.70</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2">
-        <v>4160.59</v>
+        <v>6506.00</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>375076.89</v>
+        <v>34935.56</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="2">
-        <v>11965.22</v>
+        <v>152890.98</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2">
-        <v>4008.69</v>
+        <v>1962.54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2">
-        <v>15000.00</v>
+        <v>4970.97</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2">
-        <v>1579.00</v>
+        <v>165577.70</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2">
-        <v>9177.69</v>
+        <v>12017.30</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="2">
-        <v>7462.77</v>
+        <v>53087.17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2">
-        <v>6390.74</v>
+        <v>17513.87</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2">
-        <v>36505.66</v>
+        <v>17317.81</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C14" s="2">
-        <v>2247.84</v>
+        <v>2499.65</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>8662.87</v>
+        <v>5114.06</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2">
-        <v>5645.97</v>
+        <v>5147.08</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2">
-        <v>32142.69</v>
+        <v>10326.00</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2">
-        <v>5690.30</v>
+        <v>1590.47</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>30380.38</v>
+        <v>14457.75</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="2">
-        <v>7543.03</v>
+        <v>16444.30</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>1233730.74</v>
+        <v>4160.59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="2">
-        <v>3830.80</v>
+        <v>375076.89</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>19331.46</v>
+        <v>11965.22</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="2">
-        <v>25975.73</v>
+        <v>4008.69</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C25" s="2">
-        <v>4284.80</v>
+        <v>15000.00</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2">
-        <v>1227.61</v>
+        <v>1579.00</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C27" s="2">
-        <v>7798.20</v>
+        <v>9177.69</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28" s="2">
-        <v>9542.91</v>
+        <v>7462.77</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1082,7 +1082,7 @@
         <v>49</v>
       </c>
       <c r="C29" s="2">
-        <v>34044.82</v>
+        <v>6390.74</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>72</v>
@@ -1090,16 +1090,16 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C30" s="2">
-        <v>8334.41</v>
+        <v>36505.66</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1107,10 +1107,10 @@
         <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2">
-        <v>12218.15</v>
+        <v>2247.84</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>73</v>
@@ -1121,10 +1121,10 @@
         <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" s="2">
-        <v>7950.03</v>
+        <v>8662.87</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>74</v>
@@ -1132,44 +1132,44 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="2">
-        <v>11450.53</v>
+        <v>5645.97</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C34" s="2">
-        <v>5634.22</v>
+        <v>2485.93</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C35" s="2">
-        <v>2485.93</v>
+        <v>3774.80</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1180,7 +1180,7 @@
         <v>48</v>
       </c>
       <c r="C36" s="2">
-        <v>3774.80</v>
+        <v>91907.63</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>77</v>
@@ -1188,16 +1188,16 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C37" s="2">
-        <v>91907.63</v>
+        <v>3781.30</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1208,7 +1208,7 @@
         <v>48</v>
       </c>
       <c r="C38" s="2">
-        <v>3781.30</v>
+        <v>6758.17</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>78</v>
@@ -1216,16 +1216,16 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C39" s="2">
-        <v>6758.17</v>
+        <v>3103.91</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1236,7 +1236,7 @@
         <v>48</v>
       </c>
       <c r="C40" s="2">
-        <v>3103.91</v>
+        <v>5040.84</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>79</v>
@@ -1244,16 +1244,16 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="2">
-        <v>5040.84</v>
+        <v>2739.59</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1264,7 +1264,7 @@
         <v>48</v>
       </c>
       <c r="C42" s="2">
-        <v>2739.59</v>
+        <v>8340.30</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>80</v>
@@ -1272,16 +1272,16 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C43" s="2">
-        <v>8340.30</v>
+        <v>1322.80</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="C44" s="2">
-        <v>1322.80</v>
+        <v>1548.75</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>81</v>
@@ -1300,16 +1300,16 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="2">
-        <v>1548.75</v>
+        <v>6945.50</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1320,7 +1320,7 @@
         <v>48</v>
       </c>
       <c r="C46" s="2">
-        <v>6945.50</v>
+        <v>6042.96</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>82</v>
@@ -1328,100 +1328,100 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="2">
-        <v>6042.96</v>
+        <v>0.00</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C48" s="2">
-        <v>0.00</v>
+        <v>32142.69</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>2956.97</v>
+        <v>5690.30</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C50" s="2">
-        <v>12779.70</v>
+        <v>30380.38</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="2">
-        <v>10326.00</v>
+        <v>7543.03</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C52" s="2">
-        <v>1590.47</v>
+        <v>1233730.74</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53" s="2">
-        <v>947.60</v>
+        <v>3830.80</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1429,10 +1429,10 @@
         <v>36</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C54" s="2">
-        <v>32992.40</v>
+        <v>19331.46</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>88</v>
@@ -1440,16 +1440,16 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C55" s="2">
-        <v>1102.50</v>
+        <v>25975.73</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1457,10 +1457,10 @@
         <v>37</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C56" s="2">
-        <v>20377.30</v>
+        <v>4284.80</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>89</v>
@@ -1468,16 +1468,16 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C57" s="2">
-        <v>101622.87</v>
+        <v>1227.61</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1488,7 +1488,7 @@
         <v>48</v>
       </c>
       <c r="C58" s="2">
-        <v>1408.75</v>
+        <v>7798.20</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>90</v>
@@ -1496,16 +1496,16 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C59" s="2">
-        <v>0.00</v>
+        <v>9542.91</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1513,10 +1513,10 @@
         <v>39</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C60" s="2">
-        <v>6506.00</v>
+        <v>34044.82</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>91</v>
@@ -1527,10 +1527,10 @@
         <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C61" s="2">
-        <v>34935.56</v>
+        <v>8334.41</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>92</v>
@@ -1541,10 +1541,10 @@
         <v>40</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C62" s="2">
-        <v>152890.98</v>
+        <v>12218.15</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>92</v>
@@ -1555,10 +1555,10 @@
         <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C63" s="2">
-        <v>1962.54</v>
+        <v>7950.03</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>93</v>
@@ -1569,10 +1569,10 @@
         <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C64" s="2">
-        <v>4970.97</v>
+        <v>11450.53</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>93</v>
@@ -1586,7 +1586,7 @@
         <v>49</v>
       </c>
       <c r="C65" s="2">
-        <v>165577.70</v>
+        <v>5634.22</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>94</v>
@@ -1594,86 +1594,86 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C66" s="2">
-        <v>12017.30</v>
+        <v>947.60</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C67" s="2">
-        <v>53087.17</v>
+        <v>32992.40</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C68" s="2">
-        <v>17513.87</v>
+        <v>1102.50</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C69" s="2">
-        <v>17317.81</v>
+        <v>20377.30</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C70" s="2">
-        <v>2499.65</v>
+        <v>101622.87</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C71" s="2">
-        <v>5114.06</v>
+        <v>1408.75</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1684,7 +1684,7 @@
         <v>48</v>
       </c>
       <c r="C72" s="2">
-        <v>5147.08</v>
+        <v>0.00</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>98</v>
